--- a/data/trans_bre/P12_2_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P12_2_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,55; 14,49</t>
+          <t>7,07; 14,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,58; 12,13</t>
+          <t>4,13; 12,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 14,26</t>
+          <t>4,86; 14,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 11,33</t>
+          <t>1,94; 10,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,89; 51,15</t>
+          <t>21,75; 52,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,45; 48,46</t>
+          <t>13,98; 49,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,29; 54,17</t>
+          <t>15,36; 54,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 43,94</t>
+          <t>5,89; 42,17</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 10,1</t>
+          <t>4,63; 9,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 9,2</t>
+          <t>4,38; 9,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,68</t>
+          <t>2,45; 7,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 9,09</t>
+          <t>0,6; 9,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,37; 78,58</t>
+          <t>30,93; 76,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,01; 76,95</t>
+          <t>30,75; 80,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,89; 59,98</t>
+          <t>19,62; 66,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 91,45</t>
+          <t>5,59; 95,77</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 14,2</t>
+          <t>4,14; 14,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 8,64</t>
+          <t>-1,31; 8,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 7,06</t>
+          <t>-1,31; 7,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 6,3</t>
+          <t>-1,85; 6,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,36; 109,51</t>
+          <t>23,72; 111,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 82,9</t>
+          <t>-9,19; 78,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 72,51</t>
+          <t>-9,81; 78,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 45,06</t>
+          <t>-9,65; 46,0</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,88; 12,2</t>
+          <t>8,19; 12,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,07; 10,2</t>
+          <t>6,3; 10,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,53</t>
+          <t>4,78; 8,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,05</t>
+          <t>2,01; 9,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,8; 65,85</t>
+          <t>39,95; 65,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,17; 62,45</t>
+          <t>33,98; 62,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,38; 59,17</t>
+          <t>29,11; 60,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 69,16</t>
+          <t>13,06; 68,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P12_2_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P12_2_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,81</t>
+          <t>7,27</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,07; 14,86</t>
+          <t>6,71; 14,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 12,18</t>
+          <t>3,91; 12,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 14,22</t>
+          <t>4,95; 14,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 10,87</t>
+          <t>2,88; 11,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,75; 52,77</t>
+          <t>20,96; 51,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,98; 49,35</t>
+          <t>13,37; 47,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,36; 54,24</t>
+          <t>15,91; 55,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 42,17</t>
+          <t>9,2; 45,56</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>43,23%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,66</t>
+          <t>4,61; 10,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 9,53</t>
+          <t>4,28; 9,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,14</t>
+          <t>2,47; 6,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 9,65</t>
+          <t>4,0; 8,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,93; 76,74</t>
+          <t>30,6; 80,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,75; 80,71</t>
+          <t>29,04; 76,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,62; 66,25</t>
+          <t>19,01; 63,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 95,77</t>
+          <t>25,73; 61,13</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 14,18</t>
+          <t>3,75; 14,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 8,63</t>
+          <t>-1,74; 8,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 7,4</t>
+          <t>-1,06; 6,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 6,51</t>
+          <t>-0,17; 7,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,72; 111,9</t>
+          <t>21,69; 113,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 78,67</t>
+          <t>-10,47; 76,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 78,6</t>
+          <t>-8,66; 71,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 46,0</t>
+          <t>-0,82; 56,05</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>6,6</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>39,06%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 12,3</t>
+          <t>8,19; 12,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 10,25</t>
+          <t>6,0; 10,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 8,79</t>
+          <t>4,71; 8,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 9,09</t>
+          <t>4,71; 8,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,95; 65,62</t>
+          <t>40,29; 65,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,98; 62,62</t>
+          <t>32,91; 60,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,11; 60,06</t>
+          <t>28,54; 60,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,06; 68,57</t>
+          <t>26,75; 51,71</t>
         </is>
       </c>
     </row>
